--- a/plc/s7-1x00/core/safety/ESafetyStatus-v1.0.xlsx
+++ b/plc/s7-1x00/core/safety/ESafetyStatus-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\safety\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96114D23-2E99-4772-91DC-D9377B86D496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A50B59E-4379-438F-A2CA-70BDB1AF2273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -308,7 +308,7 @@
     <t>Bool</t>
   </si>
   <si>
-    <t>{"version":"v1.0","author":"cyanezf","family":"core/safety"}</t>
+    <t>{"version":"v1.0","author":"cyanezf","family":"core/safety","status":"current","deprecatedBy":null,"dependencies":[]}</t>
   </si>
 </sst>
 </file>
